--- a/services_forms/030_service_report_rite_price--services_forms.xlsx
+++ b/services_forms/030_service_report_rite_price--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'rite_price_1',_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'rite_price_1', 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'rite_price_2',_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'rite_price_2', 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'rite_price_3',_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'rite_price_3', 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'rite_location_1',_'label':_'one'}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'rite_location_1', 'label': 'One'}</t>
+          <t>One</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'rite_location_2',_'label':_'two'}</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'rite_location_2', 'label': 'Two'}</t>
+          <t>Two</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'rite_location_3',_'label':_'three'}</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'rite_location_3', 'label': 'Three'}</t>
+          <t>Three</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy2',_'label':_'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy2', 'label': 'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'service_report_status_1',_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'service_report_status_1', 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'service_report_status_2',_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'service_report_status_2', 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'service_report_status_3',_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'service_report_status_3', 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
